--- a/02_加值成品/九上/九上4-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上4-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上4-2 電流與電路　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三上學期 九上4-2 電流與電路　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>電荷的流動稱？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>電流</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>與該燈泡串聯</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>通路</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>正極</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>流動</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>電流的單位是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>相反</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>斷路</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>電能/電壓</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>安培(A)</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>電流</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>電流要流動需形成？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>通路</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>與該燈泡串聯</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>正極</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>電路</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>電路的電源提供？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>電能/電壓</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>安培計</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>串聯</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>消耗電能做功</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>驅動</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>電流方向規定為？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>正電荷流動方向</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>串聯才能讓待測電流通過測得</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>電荷有完整路徑</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>早期規定正電荷流向,後知實為電子移動</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>規定</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>測電流的儀器是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>消耗電能做功</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>串聯</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>安培計</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>安培(A)</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>三用電表</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>安培計要怎麼接？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>電流</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>電能/電壓</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>消耗電能做功</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>串聯</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>串接</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>斷路時電流？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>流動方向</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>安培</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>通路</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>無法流動</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>中斷</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>電流方向規定為正電荷的？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>流動方向</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>串聯</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>與該燈泡串聯</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>正極</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>規定</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>電路中控制通斷的元件是？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>開關</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>斷路</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>相反</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>開關</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上4-2 電流與電路　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三上學期 九上4-2 電流與電路　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>電流方向與電子流方向？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>相反</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>通路</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>無法流動</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>安培(A)</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>規定</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>電路四要素是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>不會,是流動,能量被消耗</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>電源導線負載開關</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>正極出、負極回(外電路)</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>串聯才能讓待測電流通過測得</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>組成</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>開關斷開電路變成？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>安培計</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>開關</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>無法流動</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>斷路</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>無電流</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>安培計串聯還並聯？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>通路</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>串聯</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>相反</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>與該燈泡串聯</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>正確接法</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>電流由電源哪極經外電路流出？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>正極</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>電能/電壓</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>流動方向</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>斷路</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>規定方向</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>通路才有電流是因為？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>正電荷流動方向</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>斷路/燈絲斷/電源沒電/接觸不良</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>電荷有完整路徑</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>通路正常、斷路無流、短路電流過大</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>通路</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>電流大小用什麼單位量？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>無法流動</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>消耗電能做功</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>安培計</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>安培</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>負載在電路中的作用？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>消耗電能做功</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>安培(A)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>正極</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>流動方向</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>用電器</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>電流大小以什麼儀器測量？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>電流</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>通路</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>安培計</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>斷路</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>量電流</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>電路斷開時電流能否流動？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>斷路</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>安培</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>不能</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>安培(A)</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>斷路</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上4-2 電流與電路　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三上學期 九上4-2 電流與電路　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何安培計必須串聯而非並聯？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>正極出、負極回(外電路)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>斷路/燈絲斷/電源沒電/接觸不良</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>串聯才能讓待測電流通過測得</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>早期規定正電荷流向</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>接法</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>電流方向與電子流相反的歷史原因？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>早期規定正電荷流向,後知實為電子移動</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>電源導線負載開關</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>電路是否通、電源是否有電</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>電源—開關—燈泡成迴路</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>規定</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>一個燈泡不亮可能哪些原因？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>早期規定正電荷流向,後知實為電子移動</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>斷路/燈絲斷/電源沒電/接觸不良</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>正電荷流動方向</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>電荷有完整路徑</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>診斷</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>電流是否會在電路中被用光？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>不會,是流動,能量被消耗</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>電源—開關—燈泡成迴路</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>電源導線負載開關</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>早期規定正電荷流向</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>觀念</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>要測某燈泡電流安培計應接在？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>安培</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>安培計</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>與該燈泡串聯</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>開關</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>接法</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>通路斷路短路差異？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>通路正常、斷路無流、短路電流過大</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>電源—開關—燈泡成迴路</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>正極出、負極回(外電路)</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>串聯才能讓待測電流通過測得</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>分類</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>用電路符號畫電源燈泡開關串聯圖描述？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>電源—開關—燈泡成迴路</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>不會,是流動,能量被消耗</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>通路正常、斷路無流、短路電流過大</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>電荷有完整路徑</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>電路圖</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>電流方向如何由電源判斷？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>串聯才能讓待測電流通過測得</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>電路是否通、電源是否有電</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>不會,是流動,能量被消耗</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>正極出、負極回(外電路)</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>判斷</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何電流方向與電子實際流向相反？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>電荷有完整路徑</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>串聯才能讓待測電流通過測得</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>正電荷流動方向</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>早期規定正電荷流向</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>歷史</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>燈泡不亮應先檢查哪些(舉二)？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>電路是否通、電源是否有電</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>電源導線負載開關</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>串聯才能讓待測電流通過測得</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>斷路/燈絲斷/電源沒電/接觸不良</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>診斷</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九上/九上4-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上4-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>流動</t>
+          <t>流動：電荷在導線裡持續移動,這個現象就叫做電流</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>電流</t>
+          <t>電流：科學上用安培這個單位來表示電流的大小</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>電路</t>
+          <t>電路：電荷要能一直流動,電路必須是完整連通、沒有斷開的通路</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>驅動</t>
+          <t>驅動：電源就像幫浦一樣,提供電能推動電荷在電路中流動</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>規定</t>
+          <t>規定：科學家規定電流的方向就是正電荷移動的方向</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>三用電表</t>
+          <t>三用電表：安培計是專門用來測量電路中電流大小的儀器</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>串接</t>
+          <t>串接：安培計要接在電路中間,讓待測的電流直接通過它才能量出來</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>中斷</t>
+          <t>中斷：電路某處斷開了,電荷沒有完整路徑可走,電流就無法流動</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>規定</t>
+          <t>規定：科學上規定電流的方向是正電荷移動的方向,這是早期訂下的慣例</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>開關</t>
+          <t>開關：開關可以讓電路接通或斷開,用來控制電流是否能夠流通</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>規定</t>
+          <t>規定：電流方向定義成正電荷方向,但實際移動的是帶負電的電子,方向剛好相反</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>組成</t>
+          <t>組成：一個完整電路通常需要電源、導線、負載(用電器)和開關這四個部分</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>無電流</t>
+          <t>無電流：開關打開讓電路中斷,電荷沒辦法通過,電流就消失了</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>正確接法</t>
+          <t>正確接法：安培計必須串聯接入電路,才能讓所有電流都經過它被測到</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>規定方向</t>
+          <t>規定方向：依照規定,電流是從電源正極出發,經過外電路再流回負極</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>通路</t>
+          <t>通路：只有電路連通沒有斷開,電荷才有一條完整的路可以持續流動</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A：安培是電流大小的計量單位,符號寫作A</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>用電器</t>
+          <t>用電器：負載像燈泡馬達這類元件,會把電能轉換成光、熱或動能來做功</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>量電流</t>
+          <t>量電流：安培計(電流計)是專門用來測量電路中電流大小的儀器,單位是安培</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>斷路</t>
+          <t>斷路：電路一旦斷開(斷路),形成不了完整迴路,電流就無法流動</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>接法</t>
+          <t>接法：串聯能讓要測量的電流全部流經安培計,這樣才能正確讀出電流大小</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>規定</t>
+          <t>規定：科學家很早就先規定電流方向是正電荷方向,後來才發現真正移動的是帶負電的電子</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>診斷</t>
+          <t>診斷：可能是電路某處斷開、燈泡裡的燈絲燒斷、電池沒電了,或是接頭沒接好</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>觀念</t>
+          <t>觀念：電流本身只是電荷的流動不會消失,真正被用掉的是電荷所攜帶的能量</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>接法</t>
+          <t>接法：要量哪個元件的電流,就要把安培計串聯接在那個元件旁邊,讓電流經過它</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>分類</t>
+          <t>分類：通路是電路正常連通,斷路是電路中斷沒有電流,短路則是電流不經負載直接亂竄變得過大</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>電路圖</t>
+          <t>電路圖：把電源、開關、燈泡依序用導線接成一個封閉的迴路,電流才能流通</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>判斷</t>
+          <t>判斷：看電源符號的正負極,電流規定是從正極流出,經過外電路後再流回負極</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>歷史</t>
+          <t>歷史：科學家在還不知道電子存在時,就先規定電流方向是正電荷移動的方向;後來發現金屬導線裡實際移動的是帶負電的電子,方向剛好相反,但這個規定沿用至今</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>診斷</t>
+          <t>診斷：燈泡不亮常見原因包括電路是否接通(有沒有斷路)、電源(電池)是否還有電,這是排除故障時最先要檢查的兩個地方</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九上/九上4-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上4-2_三種難度測驗卷.xlsx
@@ -603,17 +603,17 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>相反</t>
+          <t>斷路</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>斷路</t>
+          <t>通路</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>電能/電壓</t>
+          <t>安培計</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>消耗電能做功</t>
+          <t>正極</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>串聯</t>
+          <t>與該燈泡串聯</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>安培(A)</t>
+          <t>電流</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>電流</t>
+          <t>流動方向</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>斷路</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
           <t>電能/電壓</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>消耗電能做功</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>通路</t>
+          <t>安培(A)</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>相反</t>
+          <t>電流</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>與該燈泡串聯</t>
+          <t>斷路</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>無法流動</t>
+          <t>開關</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>消耗電能做功</t>
+          <t>正極</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>安培計</t>
+          <t>電流</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>電流</t>
+          <t>開關</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>通路</t>
+          <t>安培(A)</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1560,17 +1560,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>電源導線負載開關</t>
+          <t>斷路/燈絲斷/電源沒電/接觸不良</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>電路是否通、電源是否有電</t>
+          <t>正極出、負極回(外電路)</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>電源—開關—燈泡成迴路</t>
+          <t>正電荷流動方向</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>安培</t>
+          <t>安培(A)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>安培計</t>
+          <t>無法流動</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>開關</t>
+          <t>相反</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1835,17 +1835,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
+          <t>串聯才能讓待測電流通過測得</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
           <t>電荷有完整路徑</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>串聯才能讓待測電流通過測得</t>
-        </is>
-      </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>正電荷流動方向</t>
+          <t>電源導線負載開關</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
